--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\Desktop\gtihub\Infil-V2-printer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7664C89A-9484-4781-9680-09472B45F47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EC1403-4C21-4FE4-81B7-7A313606359D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{80A16C1D-FA00-4BD1-8CF2-E7CFF0DC5DE7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{80A16C1D-FA00-4BD1-8CF2-E7CFF0DC5DE7}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN SHEET" sheetId="1" r:id="rId1"/>
     <sheet name="control board and drivers" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="90">
   <si>
     <t>MOTION</t>
   </si>
@@ -274,6 +275,39 @@
   </si>
   <si>
     <t>voron 0 bed</t>
+  </si>
+  <si>
+    <t>Length calculations</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>DESIRED</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Name / spec</t>
+  </si>
+  <si>
+    <t>MGN9C</t>
+  </si>
+  <si>
+    <t>NGN9C</t>
+  </si>
+  <si>
+    <t>MGN9H</t>
+  </si>
+  <si>
+    <t>Carridge</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -282,14 +316,6 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -334,6 +360,14 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -397,28 +431,27 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -429,9 +462,10 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -810,22 +844,22 @@
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>350</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <f>SUM(G11:G419)</f>
         <v>264.62</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <f>B5-E5</f>
         <v>85.38</v>
       </c>
@@ -851,25 +885,25 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
@@ -885,7 +919,7 @@
         <f>E13*F13</f>
         <v>21.02</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="J13" t="s">
@@ -905,7 +939,7 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J14" t="s">
@@ -925,7 +959,7 @@
       <c r="F15">
         <v>0</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J15" t="s">
@@ -949,7 +983,7 @@
         <f>E16*F16</f>
         <v>5.22</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
@@ -957,25 +991,25 @@
       </c>
     </row>
     <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="7" t="s">
+      <c r="A22" s="3"/>
+      <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
@@ -994,25 +1028,25 @@
     <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13" t="s">
+      <c r="A32" s="11"/>
+      <c r="B32" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
     </row>
     <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
@@ -1047,25 +1081,25 @@
       </c>
     </row>
     <row r="44" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A44" s="5"/>
-      <c r="B44" s="8" t="s">
+      <c r="A44" s="4"/>
+      <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
@@ -1096,25 +1130,25 @@
       </c>
     </row>
     <row r="54" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A54" s="20"/>
-      <c r="B54" s="21" t="s">
+      <c r="A54" s="19"/>
+      <c r="B54" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
-      <c r="P54" s="20"/>
-      <c r="Q54" s="20"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="19"/>
+      <c r="M54" s="19"/>
+      <c r="N54" s="19"/>
+      <c r="O54" s="19"/>
+      <c r="P54" s="19"/>
+      <c r="Q54" s="19"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
@@ -1138,25 +1172,25 @@
       </c>
     </row>
     <row r="63" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A63" s="6"/>
-      <c r="B63" s="9" t="s">
+      <c r="A63" s="5"/>
+      <c r="B63" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
@@ -1178,95 +1212,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <f>'MAIN SHEET'!E5</f>
         <v>264.62</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <f>'MAIN SHEET'!F5</f>
         <v>85.38</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="26" x14ac:dyDescent="0.6">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B6" s="19" t="b">
+      <c r="B6" s="18" t="b">
         <f>IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="19" t="b">
+      <c r="C6" s="18" t="b">
         <f>IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="19" t="b">
+      <c r="D6" s="18" t="b">
         <f>IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="19" t="b">
+      <c r="E6" s="18" t="b">
         <f t="shared" ref="E6:J8" si="0">IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="19" t="b">
+      <c r="F6" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="19" t="b">
+      <c r="G6" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="19" t="b">
+      <c r="H6" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="19" t="b">
+      <c r="I6" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="19" t="b">
+      <c r="J6" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1275,39 +1309,39 @@
       <c r="A7" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="19" t="b">
+      <c r="B7" s="18" t="b">
         <f>IF(AND(C17,C10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="19" t="b">
+      <c r="C7" s="18" t="b">
         <f>IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="19" t="b">
+      <c r="D7" s="18" t="b">
         <f>IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="19" t="b">
+      <c r="E7" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="19" t="b">
+      <c r="F7" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="19" t="b">
+      <c r="G7" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="19" t="b">
+      <c r="H7" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="19" t="b">
+      <c r="I7" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="19" t="b">
+      <c r="J7" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1325,39 +1359,39 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B8" s="19" t="b">
+      <c r="B8" s="18" t="b">
         <f>IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="19" t="b">
+      <c r="C8" s="18" t="b">
         <f>IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="19" t="b">
+      <c r="D8" s="18" t="b">
         <f>IF(AND($C$17,$C$10),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="19" t="b">
+      <c r="E8" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="19" t="b">
+      <c r="F8" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="19" t="b">
+      <c r="G8" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="19" t="b">
+      <c r="H8" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="19" t="b">
+      <c r="I8" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="19" t="b">
+      <c r="J8" s="18" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1371,7 +1405,7 @@
         <f>IF(C15,1,0)</f>
         <v>1</v>
       </c>
-      <c r="P8" s="16" t="s">
+      <c r="P8" s="15" t="s">
         <v>60</v>
       </c>
       <c r="V8">
@@ -1380,10 +1414,10 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="18" t="b">
+      <c r="C9" s="17" t="b">
         <v>1</v>
       </c>
       <c r="L9" t="s">
@@ -1396,7 +1430,7 @@
         <f>IF(C16,1,0)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="P9" s="15" t="s">
         <v>61</v>
       </c>
       <c r="V9">
@@ -1405,18 +1439,19 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="18" t="b">
+      <c r="C10" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="21" t="s">
         <v>72</v>
       </c>
+      <c r="G10" s="18"/>
       <c r="L10" t="s">
         <v>42</v>
       </c>
@@ -1427,7 +1462,7 @@
         <f>IF(C17,1,0)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="16" t="s">
+      <c r="P10" s="15" t="s">
         <v>53</v>
       </c>
       <c r="V10">
@@ -1436,14 +1471,15 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B11" s="17"/>
-      <c r="E11">
+      <c r="B11" s="16"/>
+      <c r="E11" s="18">
         <v>2</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="18">
         <f>IF(C9,4,2)</f>
         <v>4</v>
       </c>
+      <c r="G11" s="18"/>
       <c r="L11" t="s">
         <v>54</v>
       </c>
@@ -1454,7 +1490,7 @@
         <f>IF(OR(C22,(AND(C9,C17))),1,0)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="16" t="s">
+      <c r="P11" s="15" t="s">
         <v>55</v>
       </c>
       <c r="V11">
@@ -1463,16 +1499,19 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="18" t="b">
-        <v>0</v>
-      </c>
+      <c r="C12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
       <c r="L12" t="s">
         <v>43</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="16" t="s">
         <v>57</v>
       </c>
       <c r="N12">
@@ -1482,7 +1521,7 @@
         <f>IF(E15=2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="P12" s="16" t="s">
+      <c r="P12" s="15" t="s">
         <v>56</v>
       </c>
       <c r="V12">
@@ -1491,17 +1530,18 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="18" t="b">
+      <c r="C13" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="M13" s="17" t="s">
+      <c r="F13" s="21"/>
+      <c r="G13" s="18"/>
+      <c r="M13" s="16" t="s">
         <v>59</v>
       </c>
       <c r="N13">
@@ -1511,7 +1551,7 @@
         <f>IF(E16=4,1,0)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="16" t="s">
+      <c r="P13" s="15" t="s">
         <v>56</v>
       </c>
       <c r="V13">
@@ -1520,14 +1560,15 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B14" s="17"/>
-      <c r="E14">
+      <c r="B14" s="16"/>
+      <c r="E14" s="18">
         <v>2209</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="18">
         <v>5160</v>
       </c>
-      <c r="M14" s="17" t="s">
+      <c r="G14" s="18"/>
+      <c r="M14" s="16" t="s">
         <v>58</v>
       </c>
       <c r="N14">
@@ -1537,7 +1578,7 @@
         <f>IF(E16=6,1,0)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="16" t="s">
+      <c r="P14" s="15" t="s">
         <v>56</v>
       </c>
       <c r="V14">
@@ -1546,24 +1587,25 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="18" t="b">
+      <c r="C15" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="18">
         <f>E11+F11-F15</f>
         <v>2</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="18">
         <f>IF(OR(C10,C13),F11,0)</f>
         <v>4</v>
       </c>
+      <c r="G15" s="18"/>
       <c r="L15" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="17" t="s">
+      <c r="M15" s="16" t="s">
         <v>63</v>
       </c>
       <c r="N15">
@@ -1573,7 +1615,7 @@
         <f>IF(F15=2,1,0)</f>
         <v>0</v>
       </c>
-      <c r="P15" s="16" t="s">
+      <c r="P15" s="15" t="s">
         <v>62</v>
       </c>
       <c r="V15">
@@ -1582,20 +1624,22 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16">
+      <c r="C16" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="18">
         <f>IF(C17,0,E15)</f>
         <v>2</v>
       </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
       <c r="L16" t="s">
         <v>44</v>
       </c>
-      <c r="M16" s="17" t="s">
+      <c r="M16" s="16" t="s">
         <v>59</v>
       </c>
       <c r="N16">
@@ -1605,7 +1649,7 @@
         <f>IF(F15=4,1,0)</f>
         <v>1</v>
       </c>
-      <c r="P16" s="16" t="s">
+      <c r="P16" s="15" t="s">
         <v>62</v>
       </c>
       <c r="V16">
@@ -1614,12 +1658,15 @@
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="18" t="b">
-        <v>0</v>
-      </c>
+      <c r="C17" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
       <c r="L17" t="s">
         <v>48</v>
       </c>
@@ -1639,6 +1686,9 @@
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
       <c r="L18" t="s">
         <v>49</v>
       </c>
@@ -1658,10 +1708,10 @@
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="18" t="b">
+      <c r="C19" s="17" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="s">
@@ -1683,10 +1733,10 @@
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="18" t="b">
+      <c r="C20" s="17" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="s">
@@ -1708,13 +1758,13 @@
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="17" t="s">
+      <c r="C22" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="16" t="s">
         <v>74</v>
       </c>
       <c r="O22">
@@ -1723,19 +1773,19 @@
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="M32" s="17"/>
+      <c r="M32" s="16"/>
     </row>
     <row r="33" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M33" s="17"/>
+      <c r="M33" s="16"/>
     </row>
     <row r="34" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M34" s="17"/>
+      <c r="M34" s="16"/>
     </row>
     <row r="35" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M35" s="17"/>
+      <c r="M35" s="16"/>
     </row>
     <row r="36" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M36" s="17"/>
+      <c r="M36" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:J8">
@@ -1761,4 +1811,83 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D1A9DF-BF37-4E9D-AB37-3A5A4DE1BBCB}">
+  <dimension ref="B4:G15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7">
+        <v>120</v>
+      </c>
+      <c r="G7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8">
+        <v>120</v>
+      </c>
+      <c r="G8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\Desktop\gtihub\Infil-V2-printer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EC1403-4C21-4FE4-81B7-7A313606359D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BE692D-2D5A-442F-9480-507A8A357B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{80A16C1D-FA00-4BD1-8CF2-E7CFF0DC5DE7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{80A16C1D-FA00-4BD1-8CF2-E7CFF0DC5DE7}"/>
   </bookViews>
   <sheets>
-    <sheet name="MAIN SHEET" sheetId="1" r:id="rId1"/>
+    <sheet name="MAIN SHEET" sheetId="4" r:id="rId1"/>
     <sheet name="control board and drivers" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="old main" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="150">
   <si>
     <t>MOTION</t>
   </si>
@@ -277,37 +277,217 @@
     <t>voron 0 bed</t>
   </si>
   <si>
-    <t>Length calculations</t>
-  </si>
-  <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>DESIRED</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Name / spec</t>
-  </si>
-  <si>
-    <t>MGN9C</t>
-  </si>
-  <si>
-    <t>NGN9C</t>
-  </si>
-  <si>
-    <t>MGN9H</t>
-  </si>
-  <si>
-    <t>Carridge</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Y</t>
+    <t>5mm couplers</t>
+  </si>
+  <si>
+    <t>1pk</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005003594728401.html</t>
+  </si>
+  <si>
+    <t>5mm dia 250mm long , 1pcs</t>
+  </si>
+  <si>
+    <t>5mm shaft</t>
+  </si>
+  <si>
+    <t>HGX 2.0 gears + hardware</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005007316630515.html</t>
+  </si>
+  <si>
+    <t>comes with other hardware needed</t>
+  </si>
+  <si>
+    <t>m4 20 series t slot nut</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005004658668930.html</t>
+  </si>
+  <si>
+    <t>m4x24</t>
+  </si>
+  <si>
+    <t>5x5</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005008857891214.html</t>
+  </si>
+  <si>
+    <t>4015 fan</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005004832141450.html</t>
+  </si>
+  <si>
+    <t>for low speed PLA</t>
+  </si>
+  <si>
+    <t>2510 fan</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005003595630530.html</t>
+  </si>
+  <si>
+    <t>fan</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005004019523225.html</t>
+  </si>
+  <si>
+    <t>2gt 306</t>
+  </si>
+  <si>
+    <t>I allready own this</t>
+  </si>
+  <si>
+    <t>gt2 6mm closed loop belt for belt</t>
+  </si>
+  <si>
+    <t>m5x30</t>
+  </si>
+  <si>
+    <t>6 needed</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005007593838226.html</t>
+  </si>
+  <si>
+    <t>for tensioning belts</t>
+  </si>
+  <si>
+    <t>m5, 7.5mm od heatset</t>
+  </si>
+  <si>
+    <t>10pk</t>
+  </si>
+  <si>
+    <t>20pk</t>
+  </si>
+  <si>
+    <t>m5 t slot nut</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005008897571758.html</t>
+  </si>
+  <si>
+    <t>at least 26</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005007294931248.html</t>
+  </si>
+  <si>
+    <t>50pk</t>
+  </si>
+  <si>
+    <t>m3 heat sets</t>
+  </si>
+  <si>
+    <t>100pk</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005008285787978.html</t>
+  </si>
+  <si>
+    <t>IEC power inlet</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005006990146296.html</t>
+  </si>
+  <si>
+    <t>LDO 36STH20-1004AHG</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005002899860754.html</t>
+  </si>
+  <si>
+    <t>Allready own, using from infil v1</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/b/C15/BR8364/deep-groove-ball-bearing-double-side-with-dust-cover</t>
+  </si>
+  <si>
+    <t>cheaper than jlc</t>
+  </si>
+  <si>
+    <t>5mm dia 11mm shaft</t>
+  </si>
+  <si>
+    <t>5mm dia 50mm shaft</t>
+  </si>
+  <si>
+    <t>5mm dia 142mm shaft</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/B08/BACA/linear-shaft-solid-straight-g6-tolerance?k=BACA-C2G1-D5-L11&amp;productModelNumber=BACA-C2G1-D5-L%5B10~500%2F1%5D</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/B08/BACA/linear-shaft-solid-straight-g6-tolerance?k=BACA-C2G1-D5-L50&amp;productModelNumber=BACA-C2G1-D5-L%5B10~500%2F1%5D</t>
+  </si>
+  <si>
+    <t>2020 , 180mm</t>
+  </si>
+  <si>
+    <t>2020 , 320mm</t>
+  </si>
+  <si>
+    <t>2020 , 380mm</t>
+  </si>
+  <si>
+    <t>2020 , 280mm</t>
+  </si>
+  <si>
+    <t>Z1 mgn9c 314mm</t>
+  </si>
+  <si>
+    <t>Z1 mgn9c 160mm</t>
+  </si>
+  <si>
+    <t>Z1 mgn9c 224mm</t>
+  </si>
+  <si>
+    <t>external mosfet board to support the bed</t>
+  </si>
+  <si>
+    <t>using my own</t>
+  </si>
+  <si>
+    <t>Gt2 belt 2M</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005006507781085.html</t>
+  </si>
+  <si>
+    <t>I believe the printer need 2.1M of belt, I have a spare length of belt that will cover 1 of the belts</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005007347759654.html</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/T01/TXCJ/extruded-aluminum-t-slot-20-series(eu)?k=TXCJ-H7-2020D-L320&amp;productModelNumber=TXCJ-H7-2020D-L%5B50~6000%2F0.1%5D</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/T01/TXCJ/extruded-aluminum-t-slot-20-series(eu)?k=TXCJ-H7-2020D-L380&amp;productModelNumber=TXCJ-H7-2020D-L%5B50~6000%2F0.1%5D</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/T01/TXCJ/extruded-aluminum-t-slot-20-series(eu)?k=TXCJ-H7-2020D-L280&amp;productModelNumber=TXCJ-H7-2020D-L%5B50~6000%2F0.1%5D</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/T01/TXCJ/extruded-aluminum-t-slot-20-series(eu)?k=TXCJ-H7-2020D-L180&amp;productModelNumber=TXCJ-H7-2020D-L%5B50~6000%2F0.1%5D</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/B03/E-BMN/economical-linear-guide-mini-standard-type-7-9-12-15?k=E-BMN9H-1-L314-Z1-C-M-E7&amp;productModelNumber=E-BMN9H-1-L%5B45~1400%2F1%5D-Z1-C-M-E%5B0~19%2F0.5%5D</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/B03/E-BMN/economical-linear-guide-mini-standard-type-7-9-12-15?k=E-BMN9H-1-L160-Z1-C-M-E10&amp;productModelNumber=E-BMN9H-1-L%5B45~1400%2F1%5D-Z1-C-M-E%5B0~19%2F0.5%5D</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/B03/E-BMN/economical-linear-guide-mini-standard-type-7-9-12-15?k=E-BMN9H-1-L224-Z1-C-M-E12&amp;productModelNumber=E-BMN9H-1-L%5B45~1400%2F1%5D-Z1-C-M-E%5B0~19%2F0.5%5D</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/B08/BACA/linear-shaft-solid-straight-g6-tolerance?k=BACA-C2G1-D5-L142&amp;productModelNumber=BACA-C2G1-D5-L%5B10~500%2F1%5D</t>
   </si>
 </sst>
 </file>
@@ -433,7 +613,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -466,6 +646,18 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -832,10 +1024,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CAF29F-E593-4396-86FA-6DA2B5F50F4E}">
-  <dimension ref="A4:Q64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64EEADE-D7C2-44CE-B0E2-38178E72D153}">
+  <dimension ref="A4:Q156"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="3" max="3" width="11.1796875" customWidth="1"/>
     <col min="5" max="5" width="11.90625" customWidth="1"/>
     <col min="9" max="9" width="10.26953125" customWidth="1"/>
   </cols>
@@ -856,12 +1049,12 @@
         <v>350</v>
       </c>
       <c r="E5" s="9">
-        <f>SUM(G11:G419)</f>
-        <v>264.62</v>
+        <f>SUM(G11:G430)</f>
+        <v>339.44000000000005</v>
       </c>
       <c r="F5" s="9">
         <f>B5-E5</f>
-        <v>85.38</v>
+        <v>10.559999999999945</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -893,7 +1086,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -905,25 +1098,28 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G12" s="25"/>
+    </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="E13">
-        <v>21.02</v>
+        <v>5.72</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13">
-        <f>E13*F13</f>
-        <v>21.02</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>7</v>
+      <c r="G13" s="25">
+        <f t="shared" ref="G13:G23" si="0">ROUNDUP(F13*E13,2)</f>
+        <v>5.72</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="J13" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
@@ -939,6 +1135,10 @@
       <c r="F14">
         <v>0</v>
       </c>
+      <c r="G14" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I14" s="10" t="s">
         <v>18</v>
       </c>
@@ -948,256 +1148,1029 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="E15">
-        <v>15.95</v>
+        <v>0.1186</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="G15" s="25">
+        <f>ROUNDUP(F15*E15,2)</f>
+        <v>1.9</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="E16">
-        <v>5.22</v>
+        <v>1.56</v>
       </c>
       <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <f>E16*F16</f>
-        <v>5.22</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="G16" s="25">
+        <f t="shared" si="0"/>
+        <v>6.24</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="J16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A22" s="3"/>
-      <c r="B22" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17">
+        <v>0.66320000000000001</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17" s="25">
+        <f t="shared" si="0"/>
+        <v>2.6599999999999997</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18">
+        <v>0.75</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18" s="25">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19">
+        <v>1.1662999999999999</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="25">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G20" s="25"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21">
+        <v>10.951000000000001</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" s="25">
+        <f t="shared" si="0"/>
+        <v>10.959999999999999</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22">
+        <v>7.3635999999999999</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" s="25">
+        <f t="shared" si="0"/>
+        <v>14.73</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23">
+        <v>8.8442000000000007</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" s="25">
+        <f t="shared" si="0"/>
+        <v>26.540000000000003</v>
+      </c>
+      <c r="I23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G24" s="25"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G25" s="25"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G26" s="25"/>
+    </row>
+    <row r="27" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A27" s="3"/>
+      <c r="B27" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28">
+        <v>0.47120000000000001</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" s="25">
+        <f>ROUNDUP(F28*E28,2)</f>
+        <v>0.95</v>
+      </c>
+      <c r="I28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29">
+        <v>0.72719999999999996</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" s="25">
+        <f t="shared" ref="G29:G31" si="1">ROUNDUP(F29*E29,2)</f>
+        <v>1.46</v>
+      </c>
+      <c r="I29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30">
+        <v>0.98140000000000005</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30" s="25">
+        <f t="shared" si="1"/>
+        <v>1.97</v>
+      </c>
+      <c r="I30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31">
+        <v>0.82850000000000001</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" s="25">
+        <f t="shared" si="1"/>
+        <v>3.32</v>
+      </c>
+      <c r="I31" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G32" s="25"/>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G35" s="25"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G36" s="25"/>
+    </row>
+    <row r="37" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="11"/>
+      <c r="B37" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>37</v>
       </c>
-      <c r="B33" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="25"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>37</v>
       </c>
-      <c r="B34" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="25"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" s="25"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42">
+        <v>2.06</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" s="25">
+        <f>E42*F42</f>
+        <v>2.06</v>
+      </c>
+      <c r="I42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>89</v>
+      </c>
+      <c r="G43" s="25"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44">
+        <v>1.93</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" s="25">
+        <f>E44*F44</f>
+        <v>1.93</v>
+      </c>
+      <c r="I44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45">
+        <v>2.39</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" s="25">
+        <f>E45*F45</f>
+        <v>2.39</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E46">
+        <v>3.92</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="25">
+        <f>F46*E46</f>
+        <v>3.92</v>
+      </c>
+      <c r="I46" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>37</v>
       </c>
-      <c r="B36" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A44" s="4"/>
-      <c r="B44" s="7" t="s">
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47">
+        <v>3.34</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="25">
+        <f>E47*F47</f>
+        <v>3.34</v>
+      </c>
+      <c r="I47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G48" s="25"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G49" s="25"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G50" s="25"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G51" s="25"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G52" s="25"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G53" s="25"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G54" s="25"/>
+    </row>
+    <row r="55" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A55" s="4"/>
+      <c r="B55" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B45" t="s">
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
         <v>35</v>
       </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="J45" t="s">
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" s="25">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B46" t="s">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
         <v>38</v>
       </c>
-      <c r="G46">
+      <c r="G57" s="25">
         <f>'control board and drivers'!O22</f>
-        <v>173.39000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+        <v>145.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>117</v>
+      </c>
+      <c r="E58">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" s="25">
+        <f>E58*F58</f>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I58" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="E59">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" s="25">
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G60" s="25"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G61" s="25"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A54" s="19"/>
-      <c r="B54" s="20" t="s">
+      <c r="G62" s="25"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G63" s="25"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G64" s="25"/>
+    </row>
+    <row r="65" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A65" s="19"/>
+      <c r="B65" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="19"/>
-      <c r="L54" s="19"/>
-      <c r="M54" s="19"/>
-      <c r="N54" s="19"/>
-      <c r="O54" s="19"/>
-      <c r="P54" s="19"/>
-      <c r="Q54" s="19"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B55" t="s">
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="19"/>
+      <c r="O65" s="19"/>
+      <c r="P65" s="19"/>
+      <c r="Q65" s="19"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
         <v>34</v>
       </c>
-      <c r="E55">
+      <c r="E66">
         <v>64.989999999999995</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55">
-        <f>E55*F55</f>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" s="25">
+        <f>E66*F66</f>
         <v>64.989999999999995</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I66" t="s">
         <v>32</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J66" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="21" x14ac:dyDescent="0.5">
-      <c r="A63" s="5"/>
-      <c r="B63" s="8" t="s">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>84</v>
+      </c>
+      <c r="E67">
+        <v>13.85</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" s="25">
+        <f>E67*F67</f>
+        <v>13.85</v>
+      </c>
+      <c r="I67" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J67" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68">
+        <v>2.37</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" s="25">
+        <f>F68*E68</f>
+        <v>2.37</v>
+      </c>
+      <c r="I68" t="s">
+        <v>93</v>
+      </c>
+      <c r="J68" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69">
+        <v>1.62</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" s="25">
+        <f>F69*E69</f>
+        <v>1.62</v>
+      </c>
+      <c r="I69" t="s">
+        <v>96</v>
+      </c>
+      <c r="J69" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B70" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E70">
+        <v>24.42</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" s="25">
+        <v>0</v>
+      </c>
+      <c r="I70" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="J70" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G71" s="25"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G72" s="25"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G73" s="25"/>
+    </row>
+    <row r="74" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A74" s="5"/>
+      <c r="B74" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="5"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B64" t="s">
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
         <v>78</v>
       </c>
+      <c r="E75">
+        <v>13.73</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" s="25">
+        <f t="shared" ref="G70:G75" si="2">F75*E75</f>
+        <v>13.73</v>
+      </c>
+      <c r="I75" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G76" s="25"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>101</v>
+      </c>
+      <c r="E77">
+        <v>1.94</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" s="25">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>98</v>
+      </c>
+      <c r="J77" t="s">
+        <v>99</v>
+      </c>
+      <c r="K77" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G78" s="25"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G79" s="25"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="G80" s="25"/>
+    </row>
+    <row r="81" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G81" s="25"/>
+    </row>
+    <row r="82" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G82" s="25"/>
+    </row>
+    <row r="83" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G83" s="25"/>
+    </row>
+    <row r="84" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G84" s="25"/>
+    </row>
+    <row r="85" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G85" s="25"/>
+    </row>
+    <row r="86" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G86" s="25"/>
+    </row>
+    <row r="87" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G87" s="25"/>
+    </row>
+    <row r="88" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G88" s="25"/>
+    </row>
+    <row r="89" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G89" s="25"/>
+    </row>
+    <row r="90" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G90" s="25"/>
+    </row>
+    <row r="91" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G91" s="25"/>
+    </row>
+    <row r="92" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G92" s="25"/>
+    </row>
+    <row r="93" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G93" s="25"/>
+    </row>
+    <row r="94" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G94" s="25"/>
+    </row>
+    <row r="95" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G95" s="25"/>
+    </row>
+    <row r="96" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G96" s="25"/>
+    </row>
+    <row r="97" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G97" s="25"/>
+    </row>
+    <row r="98" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G98" s="25"/>
+    </row>
+    <row r="99" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G99" s="25"/>
+    </row>
+    <row r="100" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G100" s="25"/>
+    </row>
+    <row r="101" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G101" s="25"/>
+    </row>
+    <row r="102" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G102" s="25"/>
+    </row>
+    <row r="103" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G103" s="25"/>
+    </row>
+    <row r="104" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G104" s="25"/>
+    </row>
+    <row r="105" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G105" s="25"/>
+    </row>
+    <row r="106" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G106" s="25"/>
+    </row>
+    <row r="107" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G107" s="25"/>
+    </row>
+    <row r="108" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G108" s="25"/>
+    </row>
+    <row r="109" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G109" s="25"/>
+    </row>
+    <row r="110" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G110" s="25"/>
+    </row>
+    <row r="111" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G111" s="25"/>
+    </row>
+    <row r="112" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G112" s="25"/>
+    </row>
+    <row r="113" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G113" s="25"/>
+    </row>
+    <row r="114" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G114" s="25"/>
+    </row>
+    <row r="115" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G115" s="25"/>
+    </row>
+    <row r="116" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G116" s="25"/>
+    </row>
+    <row r="117" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G117" s="25"/>
+    </row>
+    <row r="118" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G118" s="25"/>
+    </row>
+    <row r="119" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G119" s="25"/>
+    </row>
+    <row r="120" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G120" s="25"/>
+    </row>
+    <row r="121" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G121" s="25"/>
+    </row>
+    <row r="122" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G122" s="25"/>
+    </row>
+    <row r="123" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G123" s="25"/>
+    </row>
+    <row r="124" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G124" s="25"/>
+    </row>
+    <row r="125" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G125" s="25"/>
+    </row>
+    <row r="126" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G126" s="25"/>
+    </row>
+    <row r="127" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G127" s="25"/>
+    </row>
+    <row r="128" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G128" s="25"/>
+    </row>
+    <row r="129" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G129" s="25"/>
+    </row>
+    <row r="130" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G130" s="25"/>
+    </row>
+    <row r="131" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G131" s="25"/>
+    </row>
+    <row r="132" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G132" s="25"/>
+    </row>
+    <row r="133" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G133" s="25"/>
+    </row>
+    <row r="134" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G134" s="25"/>
+    </row>
+    <row r="135" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G135" s="25"/>
+    </row>
+    <row r="136" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G136" s="25"/>
+    </row>
+    <row r="137" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G137" s="25"/>
+    </row>
+    <row r="138" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G138" s="25"/>
+    </row>
+    <row r="139" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G139" s="25"/>
+    </row>
+    <row r="140" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G140" s="25"/>
+    </row>
+    <row r="141" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G141" s="25"/>
+    </row>
+    <row r="142" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G142" s="25"/>
+    </row>
+    <row r="143" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G143" s="25"/>
+    </row>
+    <row r="144" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G144" s="25"/>
+    </row>
+    <row r="145" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G145" s="25"/>
+    </row>
+    <row r="146" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G146" s="25"/>
+    </row>
+    <row r="147" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G147" s="25"/>
+    </row>
+    <row r="148" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G148" s="25"/>
+    </row>
+    <row r="149" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G149" s="25"/>
+    </row>
+    <row r="150" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G150" s="25"/>
+    </row>
+    <row r="151" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G151" s="25"/>
+    </row>
+    <row r="152" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G152" s="25"/>
+    </row>
+    <row r="153" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G153" s="25"/>
+    </row>
+    <row r="154" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G154" s="25"/>
+    </row>
+    <row r="155" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G155" s="25"/>
+    </row>
+    <row r="156" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G156" s="25"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I45" r:id="rId1" xr:uid="{2C3D3AC1-58A4-41B6-91D9-D7EC78DFF675}"/>
+    <hyperlink ref="I46" r:id="rId2" xr:uid="{614C48B6-9F43-49A4-879B-891B52FF84C9}"/>
+    <hyperlink ref="I67" r:id="rId3" xr:uid="{1E435FE0-28C7-4D32-963D-43EE8AE09C44}"/>
+    <hyperlink ref="I70" r:id="rId4" xr:uid="{3F2EC9CD-DCBD-4CC7-9769-AB7EAD354F22}"/>
+    <hyperlink ref="I13" r:id="rId5" xr:uid="{AE95EC6C-C753-4E6F-84FF-4316A296D7BE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1222,11 +2195,11 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="H2" s="9">
         <f>'MAIN SHEET'!E5</f>
-        <v>264.62</v>
+        <v>339.44000000000005</v>
       </c>
       <c r="I2" s="9">
         <f>'MAIN SHEET'!F5</f>
-        <v>85.38</v>
+        <v>10.559999999999945</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="26" x14ac:dyDescent="0.6">
@@ -1443,7 +2416,7 @@
         <v>64</v>
       </c>
       <c r="C10" s="17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>71</v>
@@ -1747,14 +2720,14 @@
       </c>
       <c r="O20">
         <f>IF(AND(NOT(C19),C10),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="s">
         <v>52</v>
       </c>
       <c r="V20">
         <f t="shared" si="1"/>
-        <v>27.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.35">
@@ -1769,7 +2742,7 @@
       </c>
       <c r="O22">
         <f>SUM(V8:V20)</f>
-        <v>173.39000000000001</v>
+        <v>145.4</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.35">
@@ -1814,80 +2787,683 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D1A9DF-BF37-4E9D-AB37-3A5A4DE1BBCB}">
-  <dimension ref="B4:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CAF29F-E593-4396-86FA-6DA2B5F50F4E}">
+  <dimension ref="A4:Q72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="11.1796875" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="10.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B5" s="9">
+        <v>350</v>
+      </c>
+      <c r="E5" s="9">
+        <f>SUM(G11:G425)</f>
+        <v>279.39000000000004</v>
+      </c>
+      <c r="F5" s="9">
+        <f>B5-E5</f>
+        <v>70.609999999999957</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>21.02</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f>E13*F13</f>
+        <v>21.02</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14">
+        <v>16.14</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15">
+        <v>15.95</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>5.22</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <f>E16*F16</f>
+        <v>5.22</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17">
+        <v>1.56</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <f>E17*F17</f>
+        <v>6.24</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18">
+        <v>2.99</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <f>E18*F18</f>
+        <v>2.99</v>
+      </c>
+      <c r="I18" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="G6" t="s">
+      <c r="J18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A22" s="3"/>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="11"/>
+      <c r="B32" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7">
+      <c r="D37" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37">
+        <v>2.06</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <f>E37*F37</f>
+        <v>2.06</v>
+      </c>
+      <c r="I37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39">
+        <v>1.93</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <f>E39*F39</f>
+        <v>1.93</v>
+      </c>
+      <c r="I39" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40">
+        <v>2.39</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <f>E40*F40</f>
+        <v>2.39</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41">
+        <v>3.92</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <f>F41*E41</f>
+        <v>3.92</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E42">
+        <v>3.34</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <f>E42*F42</f>
+        <v>3.34</v>
+      </c>
+      <c r="I42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A50" s="4"/>
+      <c r="B50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="J51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>38</v>
+      </c>
+      <c r="G52">
+        <f>'control board and drivers'!O22</f>
+        <v>145.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <f>E53*F53</f>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I53" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A60" s="19"/>
+      <c r="B60" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="19"/>
+      <c r="M60" s="19"/>
+      <c r="N60" s="19"/>
+      <c r="O60" s="19"/>
+      <c r="P60" s="19"/>
+      <c r="Q60" s="19"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>34</v>
+      </c>
+      <c r="E61">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <f>E61*F61</f>
+        <v>64.989999999999995</v>
+      </c>
+      <c r="I61" t="s">
+        <v>32</v>
+      </c>
+      <c r="J61" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62">
+        <v>13.85</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <f>E62*F62</f>
+        <v>13.85</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J62" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63">
+        <v>2.37</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <f>F63*E63</f>
+        <v>2.37</v>
+      </c>
+      <c r="I63" t="s">
+        <v>93</v>
+      </c>
+      <c r="J63" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>95</v>
+      </c>
+      <c r="E64">
+        <v>1.62</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <f>F64*E64</f>
+        <v>1.62</v>
+      </c>
+      <c r="I64" t="s">
+        <v>96</v>
+      </c>
+      <c r="J64" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B65" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E65">
+        <v>24.42</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="I65" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="G7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8">
-        <v>120</v>
-      </c>
-      <c r="G8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>86</v>
+      <c r="J65" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" ht="21" x14ac:dyDescent="0.5">
+      <c r="A69" s="5"/>
+      <c r="B69" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A71" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>101</v>
+      </c>
+      <c r="E72">
+        <v>1.94</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="I72" t="s">
+        <v>98</v>
+      </c>
+      <c r="J72" t="s">
+        <v>99</v>
+      </c>
+      <c r="K72" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I18" r:id="rId1" xr:uid="{ED4F41E1-A529-4793-9FCA-84FC8970C525}"/>
+    <hyperlink ref="I40" r:id="rId2" xr:uid="{7760352D-09F6-4807-B755-17BC1DD14539}"/>
+    <hyperlink ref="I41" r:id="rId3" xr:uid="{648F2F18-4B59-4E72-AFCF-A5BBA1D16E74}"/>
+    <hyperlink ref="I62" r:id="rId4" xr:uid="{B6BC9311-9C18-4C06-915B-F634FE923818}"/>
+    <hyperlink ref="I65" r:id="rId5" xr:uid="{E92B8886-CE36-46BD-9774-3AFBD3CE6AC5}"/>
+    <hyperlink ref="I13" r:id="rId6" xr:uid="{5E77D310-E70E-4918-B67B-5E579591DE20}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\Desktop\gtihub\Infil-V2-printer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BE692D-2D5A-442F-9480-507A8A357B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FA3638-4780-4DC9-A91E-59C768B98EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{80A16C1D-FA00-4BD1-8CF2-E7CFF0DC5DE7}"/>
+    <workbookView xWindow="-28898" yWindow="-2453" windowWidth="28996" windowHeight="16396" xr2:uid="{80A16C1D-FA00-4BD1-8CF2-E7CFF0DC5DE7}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN SHEET" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="155">
   <si>
     <t>MOTION</t>
   </si>
@@ -488,6 +488,21 @@
   </si>
   <si>
     <t>https://jlcmc.com/product/s/B08/BACA/linear-shaft-solid-straight-g6-tolerance?k=BACA-C2G1-D5-L142&amp;productModelNumber=BACA-C2G1-D5-L%5B10~500%2F1%5D</t>
+  </si>
+  <si>
+    <t>removed formala as im using my own 24v psu</t>
+  </si>
+  <si>
+    <t>m4x10</t>
+  </si>
+  <si>
+    <t>at least 4</t>
+  </si>
+  <si>
+    <t>for mounting PSU</t>
+  </si>
+  <si>
+    <t>https://jlcmc.com/product/s/E02/EDLA/hex-socket-screw-full-partial-thread-standard-type-(din-912-gb-t-70.1)</t>
   </si>
 </sst>
 </file>
@@ -550,7 +565,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -599,6 +614,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -613,7 +634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -658,6 +679,7 @@
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1050,11 +1072,11 @@
       </c>
       <c r="E5" s="9">
         <f>SUM(G11:G430)</f>
-        <v>339.44000000000005</v>
+        <v>312.49000000000007</v>
       </c>
       <c r="F5" s="9">
         <f>B5-E5</f>
-        <v>10.559999999999945</v>
+        <v>37.509999999999934</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -1607,7 +1629,28 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="G48" s="25"/>
+      <c r="A48" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="F48">
+        <v>10</v>
+      </c>
+      <c r="G48" s="25">
+        <f t="shared" ref="G48" si="2">ROUNDUP(F48*E48,2)</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="I48" t="s">
+        <v>154</v>
+      </c>
+      <c r="J48" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G49" s="25"/>
@@ -1671,7 +1714,7 @@
       </c>
       <c r="G57" s="25">
         <f>'control board and drivers'!O22</f>
-        <v>145.4</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
@@ -1893,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="25">
-        <f t="shared" ref="G70:G75" si="2">F75*E75</f>
+        <f t="shared" ref="G70:G75" si="3">F75*E75</f>
         <v>13.73</v>
       </c>
       <c r="I75" t="s">
@@ -2177,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940A9813-22E6-49FD-8B3B-557C723B737C}">
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2195,11 +2238,11 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="H2" s="9">
         <f>'MAIN SHEET'!E5</f>
-        <v>339.44000000000005</v>
+        <v>312.49000000000007</v>
       </c>
       <c r="I2" s="9">
         <f>'MAIN SHEET'!F5</f>
-        <v>10.559999999999945</v>
+        <v>37.509999999999934</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="26" x14ac:dyDescent="0.6">
@@ -2372,7 +2415,7 @@
         <v>40</v>
       </c>
       <c r="N8">
-        <v>26.46</v>
+        <v>24.03</v>
       </c>
       <c r="O8">
         <f>IF(C15,1,0)</f>
@@ -2383,7 +2426,7 @@
       </c>
       <c r="V8">
         <f>O8*N8</f>
-        <v>26.46</v>
+        <v>24.03</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
@@ -2488,7 +2531,7 @@
         <v>57</v>
       </c>
       <c r="N12">
-        <v>8.35</v>
+        <v>7.39</v>
       </c>
       <c r="O12">
         <f>IF(E15=2,1,0)</f>
@@ -2499,7 +2542,7 @@
       </c>
       <c r="V12">
         <f t="shared" si="1"/>
-        <v>8.35</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
@@ -2582,7 +2625,8 @@
         <v>63</v>
       </c>
       <c r="N15">
-        <v>47.76</v>
+        <f>21.72*2</f>
+        <v>43.44</v>
       </c>
       <c r="O15">
         <f>IF(F15=2,1,0)</f>
@@ -2616,7 +2660,8 @@
         <v>59</v>
       </c>
       <c r="N16">
-        <v>82.6</v>
+        <f>21.72*4</f>
+        <v>86.88</v>
       </c>
       <c r="O16">
         <f>IF(F15=4,1,0)</f>
@@ -2627,10 +2672,10 @@
       </c>
       <c r="V16">
         <f t="shared" si="1"/>
-        <v>82.6</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.35">
+        <v>86.88</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B17" s="16" t="s">
         <v>42</v>
       </c>
@@ -2658,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.35">
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
@@ -2680,7 +2725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B19" s="16" t="s">
         <v>66</v>
       </c>
@@ -2691,21 +2736,23 @@
         <v>51</v>
       </c>
       <c r="N19">
-        <v>27.99</v>
+        <v>29.91</v>
       </c>
       <c r="O19">
         <f>IF(C20,0,1)</f>
         <v>1</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="V19">
-        <f t="shared" si="1"/>
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="V19" s="30">
+        <v>0</v>
+      </c>
+      <c r="W19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B20" s="16" t="s">
         <v>67</v>
       </c>
@@ -2716,7 +2763,7 @@
         <v>50</v>
       </c>
       <c r="N20">
-        <v>27.99</v>
+        <v>29.91</v>
       </c>
       <c r="O20">
         <f>IF(AND(NOT(C19),C10),1,0)</f>
@@ -2730,7 +2777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B22" s="16" t="s">
         <v>70</v>
       </c>
@@ -2742,10 +2789,10 @@
       </c>
       <c r="O22">
         <f>SUM(V8:V20)</f>
-        <v>145.4</v>
-      </c>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.35">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.35">
       <c r="M32" s="16"/>
     </row>
     <row r="33" spans="13:13" x14ac:dyDescent="0.35">
@@ -2781,6 +2828,7 @@
     <hyperlink ref="P9" r:id="rId7" xr:uid="{B1012C89-8D3C-4135-851C-F401BDBFBD8B}"/>
     <hyperlink ref="P15" r:id="rId8" xr:uid="{16ABB29F-7814-4DB7-9BD4-9015F98A6FF2}"/>
     <hyperlink ref="P16" r:id="rId9" xr:uid="{A1FA4F46-9C3D-4E88-9D25-0DE59ED5455F}"/>
+    <hyperlink ref="P19" r:id="rId10" xr:uid="{A201F503-0885-4402-8681-AC26B9A7C801}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2813,11 +2861,11 @@
       </c>
       <c r="E5" s="9">
         <f>SUM(G11:G425)</f>
-        <v>279.39000000000004</v>
+        <v>252.29</v>
       </c>
       <c r="F5" s="9">
         <f>B5-E5</f>
-        <v>70.609999999999957</v>
+        <v>97.710000000000008</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -3250,7 +3298,7 @@
       </c>
       <c r="G52">
         <f>'control board and drivers'!O22</f>
-        <v>145.4</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
